--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/dic-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/dic-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>13471.12</v>
+        <v>13296.99</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>21482.8</v>
+        <v>21205.13</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12139.48</v>
+        <v>11985.28</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>22102.56</v>
+        <v>21821.81</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8001.17</v>
+        <v>7899.53</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8106.53</v>
+        <v>8025.87</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10779.15</v>
+        <v>10671.9</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13924.72</v>
+        <v>13874.79</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8936.709999999999</v>
+        <v>8904.67</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8224.809999999999</v>
+        <v>8207.01</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9240.99</v>
+        <v>9220.99</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>13901.65</v>
+        <v>13871.56</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8607.84</v>
+        <v>8589.209999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8094.55</v>
+        <v>8077.03</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>26317.89</v>
+        <v>26260.93</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12803.4</v>
+        <v>12655.22</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>15146.42</v>
+        <v>14971.12</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17573.16</v>
+        <v>17369.78</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>17924.96</v>
+        <v>17717.51</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13644.09</v>
+        <v>13486.18</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>10068.73</v>
+        <v>9952.200000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>11242.33</v>
+        <v>11147.1</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>52239.59</v>
+        <v>51797.08</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>15777.24</v>
+        <v>15643.59</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>20929.69</v>
+        <v>20912.86</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6368.01</v>
+        <v>6362.89</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>14442.5</v>
+        <v>14430.89</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9053.299999999999</v>
+        <v>9046.02</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8845.02</v>
+        <v>8837.91</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6322.95</v>
+        <v>6317.86</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7615.88</v>
+        <v>7645.11</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7508.76</v>
+        <v>7537.58</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>34174.31</v>
+        <v>34305.48</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>13143.96</v>
+        <v>13194.41</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7567.22</v>
+        <v>7596.26</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>6419.07</v>
+        <v>6443.7</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>9070.530000000001</v>
+        <v>9111.629999999999</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>44332.26</v>
+        <v>44533.16</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>15523.1</v>
+        <v>15593.45</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>10740.52</v>
+        <v>10789.19</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5520.31</v>
+        <v>5545.32</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7006.4</v>
+        <v>7038.15</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>48262.08</v>
+        <v>48480.79</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>11137.31</v>
+        <v>11166.84</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8360.280000000001</v>
+        <v>8382.450000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>17248.18</v>
+        <v>17223.98</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8316.879999999999</v>
+        <v>8305.209999999999</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>11089.19</v>
+        <v>11073.63</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>14002.04</v>
+        <v>14019.99</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11088.98</v>
+        <v>11103.2</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>64016.23</v>
+        <v>64098.29</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>13910.57</v>
+        <v>13928.4</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>28751.98</v>
+        <v>28788.84</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>46205.84</v>
+        <v>46265.07</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>19122</v>
+        <v>19253.62</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>16650.57</v>
+        <v>16765.18</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7728.43</v>
+        <v>7781.62</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>57762.43</v>
+        <v>58160.02</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>15719.58</v>
+        <v>15827.78</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>77948.14999999999</v>
+        <v>78484.67999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>17732.62</v>
+        <v>17854.68</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>36753.47</v>
+        <v>37006.46</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>13237.85</v>
+        <v>13328.97</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>21179.18</v>
+        <v>21324.96</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>19000.69</v>
+        <v>19131.48</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>9943.059999999999</v>
+        <v>10011.5</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6323.08</v>
+        <v>6366.61</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>12734.25</v>
+        <v>12821.9</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>13421.13</v>
+        <v>13513.51</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5484.98</v>
+        <v>5531.85</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>27276.81</v>
+        <v>27509.91</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>37043.46</v>
+        <v>37360.03</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>9430.299999999999</v>
+        <v>9510.889999999999</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>69235.67999999999</v>
+        <v>69978.34</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>17388.96</v>
+        <v>17575.49</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>6091.82</v>
+        <v>6157.16</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>58739.57</v>
+        <v>59369.64</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>7673.64</v>
+        <v>7755.95</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>64254.38</v>
+        <v>64943.61</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>21393.57</v>
+        <v>21656.5</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>8141.35</v>
+        <v>8241.4</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>12601.16</v>
+        <v>12670.07</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>17466.51</v>
+        <v>17562.03</v>
       </c>
     </row>
     <row r="85">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>6367.4</v>
+        <v>6402.22</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>63218.68</v>
+        <v>63564.4</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>49009.87</v>
+        <v>49277.9</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>14235.76</v>
+        <v>14313.62</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>19182.09</v>
+        <v>19286.99</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>9091.52</v>
+        <v>9141.23</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/dic-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/dic-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/dic-2025.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>PLUSMEDICAL SPA</t>
+          <t>Plusmedical SpA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/dic-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/dic-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -941,7 +965,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3265-2149-CM25</t>
+          <t>4642-2803-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,48 +985,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>60.514.000-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13874.79</v>
+        <v>8904.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4642-2803-CM25</t>
+          <t>3265-2149-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,48 +1050,52 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.514.000-9</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8904.67</v>
+        <v>13874.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>318-184-CM25</t>
+          <t>1339163-83-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,32 +1115,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.816.800-9</t>
+          <t>61.981.070-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORP DE ASISTENCIA JUDICIAL DE LA REGION DE VALPARAISO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1150,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8207.01</v>
+        <v>8077.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>692249-20-CM25</t>
+          <t>1057780-122-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,43 +1181,47 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9220.99</v>
+        <v>8589.209999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1177296-555-CM25</t>
+          <t>1736-4055-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1246,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.255.300-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,28 +1261,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>13871.56</v>
+        <v>26260.93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057780-122-CM25</t>
+          <t>1177296-555-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,27 +1311,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1341,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8589.209999999999</v>
+        <v>13871.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1339163-83-CM25</t>
+          <t>692249-20-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,12 +1372,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.981.070-8</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1387,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1402,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8077.03</v>
+        <v>9220.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1736-4055-CM25</t>
+          <t>318-184-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,48 +1428,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.255.300-4</t>
+          <t>70.816.800-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>26260.93</v>
+        <v>8207.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2934-137-CM25</t>
+          <t>1293138-368-SE25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1488,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1498,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.073.200-9</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALHUE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,28 +1513,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12655.22</v>
+        <v>76427.21000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057780-120-CM25</t>
+          <t>2852-1307-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,43 +1563,47 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>14971.12</v>
+        <v>9952.200000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1049-2221-CM25</t>
+          <t>4642-2813-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,43 +1628,47 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.310.000-8</t>
+          <t>60.514.000-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>INSTITUTO DE FOMENTO PESQUERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17369.78</v>
+        <v>13486.18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>697058-99-CM25</t>
+          <t>2934-137-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1632,17 +1688,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,28 +1708,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>17717.51</v>
+        <v>12655.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4642-2813-CM25</t>
+          <t>1049-2221-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,27 +1758,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.514.000-9</t>
+          <t>61.310.000-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO DE FOMENTO PESQUERO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1788,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13486.18</v>
+        <v>17369.78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2852-1307-CM25</t>
+          <t>1057780-120-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,27 +1819,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1849,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9952.200000000001</v>
+        <v>14971.12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>839-32-CM25</t>
+          <t>697058-99-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,27 +1870,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1843,14 +1903,18 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>11147.1</v>
+        <v>17717.51</v>
       </c>
     </row>
     <row r="24">
@@ -1978,7 +2042,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2069-20578-CM25</t>
+          <t>839-32-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +2057,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,43 +2067,47 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>suria ltda</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.827.520-1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>20912.86</v>
+        <v>11147.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2181-334-CM25</t>
+          <t>2069-20578-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,32 +2127,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.827.520-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2162,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6362.89</v>
+        <v>20912.86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>886182-300-CM25</t>
+          <t>2181-334-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,32 +2188,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2223,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>14430.89</v>
+        <v>6362.89</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1195104-407-CM25</t>
+          <t>886182-300-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,43 +2254,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62.000.920-2</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9046.02</v>
+        <v>14430.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1232565-498-CM25</t>
+          <t>1195104-407-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,43 +2319,47 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>62.000.920-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8837.91</v>
+        <v>9046.02</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>707418-229-CM25</t>
+          <t>1232565-498-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,17 +2379,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,28 +2399,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6317.86</v>
+        <v>8837.91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>883-221-CM25</t>
+          <t>707418-229-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,53 +2439,57 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7645.11</v>
+        <v>6317.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1293138-370-CM25</t>
+          <t>4629-819-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2425,17 +2509,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2529,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7537.58</v>
+        <v>6443.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5952-456-CM25</t>
+          <t>948354-1689-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,42 +2574,46 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>MUEBLES MELINA SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>77.472.821-K</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>34305.48</v>
+        <v>7596.26</v>
       </c>
     </row>
     <row r="35">
@@ -2575,7 +2667,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2588,7 +2684,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>948354-1689-CM25</t>
+          <t>1293138-370-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,17 +2704,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2724,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MUEBLES MELINA SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.472.821-K</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2739,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7596.26</v>
+        <v>7537.58</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4629-819-CM25</t>
+          <t>5952-456-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2669,32 +2765,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2800,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>6443.7</v>
+        <v>34305.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1968-3290-CM25</t>
+          <t>883-221-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,37 +2821,37 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2861,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>9111.629999999999</v>
+        <v>7645.11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>591-7694-CM25</t>
+          <t>3232-757-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2791,48 +2887,52 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>44533.16</v>
+        <v>15593.45</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3232-757-CM25</t>
+          <t>2348-1647-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,32 +2952,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>IDEA MARKET SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.148.288-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,7 +2987,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>15593.45</v>
+        <v>5545.32</v>
       </c>
     </row>
     <row r="41">
@@ -2941,7 +3041,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2954,7 +3058,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2348-1647-CM25</t>
+          <t>629373-422-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,43 +3083,47 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>70.962.500-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>IDEA MARKET SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.148.288-2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5545.32</v>
+        <v>7038.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>629373-422-CM25</t>
+          <t>591-7694-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,43 +3148,47 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.962.500-4</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7038.15</v>
+        <v>44533.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1469-4213-CM25</t>
+          <t>1968-3290-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,43 +3213,47 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>48480.79</v>
+        <v>9111.629999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1208102-83-CM25</t>
+          <t>1469-4213-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,22 +3268,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3293,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.625.647-3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3308,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>11166.84</v>
+        <v>48480.79</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2176-623-CM25</t>
+          <t>1208102-83-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3218,48 +3334,52 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8382.450000000001</v>
+        <v>11166.84</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1095439-18-CM25</t>
+          <t>2176-623-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,53 +3394,57 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>17223.98</v>
+        <v>8382.450000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5067-3410-CM25</t>
+          <t>1095439-18-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,43 +3469,47 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8305.209999999999</v>
+        <v>17223.98</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2832-5545-CM25</t>
+          <t>5067-3410-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,48 +3529,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.260.400-8</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>11073.63</v>
+        <v>8305.209999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4629-822-CM25</t>
+          <t>2832-5545-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,53 +3589,57 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.260.400-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>MUEBLES TIMAUKEL LIMITADA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.042.830-9</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>14019.99</v>
+        <v>11073.63</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2366-4453-CM25</t>
+          <t>4629-822-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3528,27 +3664,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MUEBLES TIMAUKEL LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.042.830-9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3694,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11103.2</v>
+        <v>14019.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5153-2715-CM25</t>
+          <t>2366-4453-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3584,48 +3720,52 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>64098.29</v>
+        <v>11103.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1968-3314-CM25</t>
+          <t>5153-2715-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,48 +3785,52 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>13928.4</v>
+        <v>64098.29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>634-1131-CM25</t>
+          <t>1968-3314-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3711,7 +3855,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.004.000-4</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3721,17 +3865,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3885,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>28788.84</v>
+        <v>13928.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057448-675-CM25</t>
+          <t>634-1131-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3772,43 +3916,47 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.004.000-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>46265.07</v>
+        <v>28788.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1495199-3-CM25</t>
+          <t>1057448-675-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3971,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3981,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,28 +3996,32 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>19253.62</v>
+        <v>46265.07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1495202-3-SE25</t>
+          <t>1495199-3-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3904,7 +4056,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3928,13 +4080,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>16765.18</v>
+        <v>19253.62</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1016414-189-CM25</t>
+          <t>1385462-296-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3959,12 +4111,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.909.000-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE TELEVISION</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,28 +4126,32 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7781.62</v>
+        <v>37006.46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2429-3187-CM25</t>
+          <t>1016414-189-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4015,22 +4171,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>60.909.000-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4043,20 +4199,24 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>58160.02</v>
+        <v>7781.62</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1495205-3-CM25</t>
+          <t>2429-3187-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4076,48 +4236,52 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>15827.78</v>
+        <v>58160.02</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1186229-388-CM25</t>
+          <t>1495205-3-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4142,43 +4306,47 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.007.474-8</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>78484.67999999999</v>
+        <v>15827.78</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1495207-5-CM25</t>
+          <t>1186229-388-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4203,27 +4371,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.007.474-8</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,13 +4401,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>17854.68</v>
+        <v>78484.67999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1385462-296-CM25</t>
+          <t>1495207-5-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4274,7 +4442,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4287,20 +4455,24 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>37006.46</v>
+        <v>17854.68</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1495203-6-CM25</t>
+          <t>1495202-3-SE25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4335,7 +4507,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4348,20 +4520,24 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>13328.97</v>
+        <v>16765.18</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1494998-5-CM25</t>
+          <t>1495203-6-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4396,7 +4572,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4409,20 +4585,24 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>21324.96</v>
+        <v>13328.97</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1495200-5-CM25</t>
+          <t>1494998-5-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4457,7 +4637,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4470,20 +4650,24 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>19131.48</v>
+        <v>21324.96</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2410-2656-CM25</t>
+          <t>1495200-5-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4508,17 +4692,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4531,20 +4715,24 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>10011.5</v>
+        <v>19131.48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2410-2655-CM25</t>
+          <t>2410-2656-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4592,20 +4780,24 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6366.61</v>
+        <v>10011.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2410-2654-CM25</t>
+          <t>2410-2655-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4645,28 +4837,32 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>12821.9</v>
+        <v>6366.61</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1495209-4-CM25</t>
+          <t>2410-2654-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4691,27 +4887,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4721,13 +4917,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>13513.51</v>
+        <v>12821.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>591-7711-CM25</t>
+          <t>1495209-4-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4742,53 +4938,57 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5531.85</v>
+        <v>13513.51</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>564162-1484-CM25</t>
+          <t>591-7711-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4808,17 +5008,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,28 +5028,32 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>27509.91</v>
+        <v>5531.85</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3453-679-CM25</t>
+          <t>564162-1484-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4874,12 +5078,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4889,28 +5093,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>MUNDO LOCKERS SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.580.205-9</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>37360.03</v>
+        <v>27509.91</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1563-93-CM25</t>
+          <t>3453-679-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4935,27 +5143,27 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>MUNDO LOCKERS SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.580.205-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4965,13 +5173,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>9510.889999999999</v>
+        <v>37360.03</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3762-3515-CM25</t>
+          <t>1563-93-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4986,37 +5194,37 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5026,13 +5234,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>69978.34</v>
+        <v>9510.889999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1208107-103-CM25</t>
+          <t>3762-3515-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5052,22 +5260,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5080,20 +5288,24 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>17575.49</v>
+        <v>69978.34</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1177296-589-CM25</t>
+          <t>1208107-103-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5128,33 +5340,37 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>IMPORTADORA FULLMUEBLES SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.351.814-9</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>6157.16</v>
+        <v>17575.49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1210674-294-CM25</t>
+          <t>1177296-589-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5194,22 +5410,26 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>BODEGA STOCK SPA</t>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.744.548-2</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+          <t>77.351.814-9</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>59369.64</v>
+        <v>6157.16</v>
       </c>
     </row>
     <row r="79">
@@ -5263,7 +5483,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5276,7 +5500,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1186229-393-CM25</t>
+          <t>1210674-294-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5301,12 +5525,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5316,12 +5540,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>MODUS Design Limitada</t>
+          <t>BODEGA STOCK SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>79.893.240-3</t>
+          <t>76.744.548-2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5331,13 +5555,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>64943.61</v>
+        <v>59369.64</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3608-767-CM25</t>
+          <t>1186229-393-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5352,37 +5576,37 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>MODUS Design Limitada</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
+          <t>79.893.240-3</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5392,13 +5616,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>21656.5</v>
+        <v>64943.61</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1057056-52-CM25</t>
+          <t>3608-767-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5418,32 +5642,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Plusmedical SpA</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.520.087-3</t>
+          <t>76.675.854-1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5453,13 +5677,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>8241.4</v>
+        <v>21656.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>316-978-CM25</t>
+          <t>948354-1755-SE25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5474,53 +5698,57 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>12670.07</v>
+        <v>1119027.29</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5403-85-CM25</t>
+          <t>1057056-52-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5535,7 +5763,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5545,12 +5773,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5560,12 +5788,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>Plusmedical SpA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.520.087-3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5575,13 +5803,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>17562.03</v>
+        <v>8241.4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3776-781-CM25</t>
+          <t>316-978-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5606,12 +5834,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5621,12 +5849,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5636,13 +5864,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>6402.22</v>
+        <v>12670.07</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1475044-21-CM25</t>
+          <t>5403-85-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5667,12 +5895,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.978.810-9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>COMISION NACIONAL DE ACREDITACION</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5682,28 +5910,32 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>63564.4</v>
+        <v>17562.03</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1186229-392-CM25</t>
+          <t>3776-781-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5718,53 +5950,57 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>49277.9</v>
+        <v>6402.22</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1260060-25-CM25</t>
+          <t>1475044-21-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5779,7 +6015,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5789,12 +6025,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.602.121-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5804,12 +6040,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5819,13 +6055,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>14313.62</v>
+        <v>63564.4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1216062-1170-CM25</t>
+          <t>1186229-392-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5850,12 +6086,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5865,12 +6101,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.675.854-1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5880,13 +6116,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>19286.99</v>
+        <v>49277.9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1057858-26-CM25</t>
+          <t>1260060-25-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5911,12 +6147,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.608.600-6</t>
+          <t>61.602.121-4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5926,12 +6162,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5941,6 +6177,136 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
+        <v>14313.62</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1216062-1170-CM25</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>71.265.200-4</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Corporación Municipal de Lo Prado</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>19286.99</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1057858-26-CM25</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>61.608.600-6</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
         <v>9141.23</v>
       </c>
     </row>
